--- a/ig/nr-add-MS-device-method/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
+++ b/ig/nr-add-MS-device-method/StructureDefinition-mesures-bundle-flux-alimentation.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:47:06+00:00</t>
+    <t>2023-11-28T13:04:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
